--- a/stories/arbres/ATOM-SAN.HYG.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Agathe sort des toilettes. Maman est près du lavabo. Maman dit : après les toilettes, on lave. Agathe ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent la fleur. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Agathe va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Maman dit : savon et eau. Après les toilettes. Avant de manger aussi. Agathe sourit. Ses mains sentent le savon.</t>
+          <t>Agathe sort des toilettes. Maman est près du lavabo. Après les toilettes, on lave. Agathe ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent la fleur. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Agathe va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Agathe sourit. Ses mains sentent le savon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Agathe sort des toilettes. Maman est près du lavabo.
+maman|Après les toilettes, on lave.
+narrateur|Agathe ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent la fleur. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Agathe va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie.
+maman|Savon et eau. Après les toilettes. Avant de manger aussi.
+narrateur|Agathe sourit. Ses mains sentent le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Agathe se lave les mains. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Après les toilettes, Agathe a lavé. Avant de manger, Agathe a lavé. Savon et eau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Agathe s'assoit près de maman. Ses mains sont propres.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Agathe sourit. Ses mains sentent le savon.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Agathe se lave les mains. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Après les toilettes, Agathe a lavé. Avant de manger, Agathe a lavé. Savon et eau.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Agathe s'assoit près de maman. Ses mains sont propres.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agathe lave ses mains</t>
+          <t>Le savon fleur de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le miroir est embué. Nina se lave au savon fleur après les toilettes, puis encore avant de manger. Ses mains sentent la fleur.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Agathe sort des toilettes. Maman est près du lavabo. Après les toilettes, on lave. Agathe ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent la fleur. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Agathe va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Agathe sourit. Ses mains sentent le savon.</t>
+          <t>Le miroir est tout embué. Un petit canard jaune attend. Les carreaux sont tièdes. Ça sent un peu le savon. Une petite lampe fait un rond. Le tapis de bain est doux. Une goutte fait ploc. Nina, je suis près du lavabo. J'arrive, maman. Tu vois le canard jaune ? Oui. Il attend. En ce moment, Nina sort. Elle sort des toilettes. Après les toilettes, on lave. Je prends le savon. Nina ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent la fleur. Ça sent la fleur. Oui. Frotte tes mains. Nina frotte ses mains. Elle frotte le dessus. Elle frotte le dessous. Elle rince. Les bulles partent. Elle essuie. Les mains sont propres. Bravo, Nina. Tu as fait du bon travail. Mes mains sentent la fleur. Oui. C'est le savon. Plus tard, ça sent le repas. La cuisine est un peu chaude. C'est l'heure de manger. Avant de manger, on lave. Je vais au lavabo. Nina ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Savon et eau. Tu as fini tes mains ? Oui, maman. Bravo. Nina sourit. Ses mains sentent le savon. Le petit canard attend encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Agathe sort des toilettes. Maman est près du lavabo.
+          <t>narrateur|Le miroir est tout embué.
+narrateur|Un petit canard jaune attend.
+narrateur|Les carreaux sont tièdes.
+narrateur|Ça sent un peu le savon.
+narrateur|Une petite lampe fait un rond.
+narrateur|Le tapis de bain est doux.
+narrateur|Une goutte fait ploc.
+maman|Nina, je suis près du lavabo.
+enfant-f|J'arrive, maman.
+maman|Tu vois le canard jaune ?
+enfant-f|Oui. Il attend.
+narrateur|En ce moment, Nina sort.
+narrateur|Elle sort des toilettes.
 maman|Après les toilettes, on lave.
-narrateur|Agathe ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent la fleur. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Agathe va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie.
-maman|Savon et eau. Après les toilettes. Avant de manger aussi.
-narrateur|Agathe sourit. Ses mains sentent le savon.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Je prends le savon.
+narrateur|Nina ouvre l'eau.
+narrateur|L'eau est tiède.
+narrateur|Elle prend le savon.
+narrateur|Le savon sent la fleur.
+enfant-f|Ça sent la fleur.
+maman|Oui. Frotte tes mains.
+narrateur|Nina frotte ses mains.
+narrateur|Elle frotte le dessus.
+narrateur|Elle frotte le dessous.
+narrateur|Elle rince.
+narrateur|Les bulles partent.
+narrateur|Elle essuie.
+narrateur|Les mains sont propres.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+enfant-f|Mes mains sentent la fleur.
+maman|Oui. C'est le savon.
+narrateur|Plus tard, ça sent le repas.
+narrateur|La cuisine est un peu chaude.
+maman|C'est l'heure de manger.
+maman|Avant de manger, on lave.
+enfant-f|Je vais au lavabo.
+narrateur|Nina ouvre l'eau.
+narrateur|Elle prend le savon.
+narrateur|Elle frotte.
+narrateur|Elle rince.
+narrateur|Elle essuie.
+maman|Savon et eau.
+maman|Après les toilettes.
+maman|Avant de manger aussi.
+enfant-f|Savon et eau.
+maman|Tu as fini tes mains ?
+enfant-f|Oui, maman.
+maman|Bravo.
+narrateur|Nina sourit.
+narrateur|Ses mains sentent le savon.
+narrateur|Le petit canard attend encore.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Agathe se lave les mains. Avec quoi ?</t>
+          <t>Nina se lave les mains. Avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1562,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Agathe se lave les mains. Avec quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina se lave les mains.
+narrateur|Avec quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Après les toilettes, Agathe a lavé. Avant de manger, Agathe a lavé. Savon et eau.</t>
+          <t>Après les toilettes, Nina a lavé. Avant de manger, Nina a lavé. Savon et eau. Tu te souviens du savon fleur ? Oui. Savon et eau. Bravo, Nina. Le petit canard attend encore. Le miroir est moins embué. Le tapis de bain est encore doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1734,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Après les toilettes, Agathe a lavé. Avant de manger, Agathe a lavé. Savon et eau.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Après les toilettes, Nina a lavé.
+narrateur|Avant de manger, Nina a lavé.
+narrateur|Savon et eau.
+maman|Tu te souviens du savon fleur ?
+enfant-f|Oui. Savon et eau.
+maman|Bravo, Nina.
+narrateur|Le petit canard attend encore.
+narrateur|Le miroir est moins embué.
+narrateur|Le tapis de bain est encore doux.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Agathe s'assoit près de maman. Ses mains sont propres.</t>
+          <t>Nina s'assoit près de maman. Ses mains sont propres. Tu as les mains propres ? Oui, maman. Bravo. On mange. L'assiette est tiède. Ça sent bon. Mes mains sentent la fleur. Oui. C'est le savon. La petite lampe fait encore un rond.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1909,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Agathe s'assoit près de maman. Ses mains sont propres.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina s'assoit près de maman.
+narrateur|Ses mains sont propres.
+maman|Tu as les mains propres ?
+enfant-f|Oui, maman.
+maman|Bravo. On mange.
+narrateur|L'assiette est tiède.
+narrateur|Ça sent bon.
+enfant-f|Mes mains sentent la fleur.
+maman|Oui. C'est le savon.
+narrateur|La petite lampe fait encore un rond.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1945,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a lavé après les toilettes. Nina a lavé avant de manger. Bravo, Nina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2085,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nina a lavé après les toilettes.
+narrateur|Nina a lavé avant de manger.
+maman|Bravo, Nina.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2147,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le miroir est tout embué. Un petit canard jaune attend. Les carreaux sont tièdes. Ça sent un peu le savon. Une petite lampe fait un rond. Le tapis de bain est doux. Une goutte fait ploc. Nina, je suis près du lavabo. J'arrive, maman. Tu vois le canard jaune ? Oui. Il attend. En ce moment, Nina sort. Elle sort des toilettes. Après les toilettes, on lave. Je prends le savon. Nina ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent la fleur. Ça sent la fleur. Oui. Frotte tes mains. Nina frotte ses mains. Elle frotte le dessus. Elle frotte le dessous. Elle rince. Les bulles partent. Elle essuie. Les mains sont propres. Bravo, Nina. Tu as fait du bon travail. Mes mains sentent la fleur. Oui. C'est le savon. Plus tard, ça sent le repas. La cuisine est un peu chaude. C'est l'heure de manger. Avant de manger, on lave. Je vais au lavabo. Nina ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Savon et eau. Tu as fini tes mains ? Oui, maman. Bravo. Nina sourit. Ses mains sentent le savon. Le petit canard attend encore.</t>
+          <t>Le miroir est tout embué. Un petit canard jaune attend. Les carreaux sont tièdes. Ça sent un peu le savon. Une petite lampe fait un rond. Le tapis de bain est doux. Une goutte fait ploc. Nina, viens. Le lavabo est prêt. J'arrive, maman. Tu vois le canard jaune ? Oui. Il attend. En ce moment, Nina sort. Elle sort des toilettes. Après les toilettes, on lave. Je prends le savon. Nina ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent la fleur. Ça sent la fleur. Oui. Frotte tes mains. Nina frotte ses mains. Elle frotte le dessus. Elle frotte le dessous. Elle rince. Les bulles partent. Elle essuie. Les mains sont propres. Bravo, Nina. Mes mains sentent la fleur. Oui. C'est le savon. Nina touche le miroir embué. Elle dessine un petit rond. Tu as fait un rond ? Oui, maman. Il est joli. Plus tard, ça sent le repas. La cuisine est un peu chaude. C'est l'heure de manger. Avant de manger, on lave. Je vais au lavabo. Nina ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Savon et eau. Tu as fini tes mains ? Oui, maman. Bravo. Nina regarde ses mains. Ses mains sentent le savon. Le petit canard attend encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Agathe sort des toilettes. Maman est près du lavabo. Maman dit : après les toilettes, on lave. Agathe ouvre l'eau. L'eau est tiède. Elle prend le &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt;. Le savon sent la fleur. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Agathe va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Maman dit : savon et eau. Après les toilettes. Avant de manger aussi. Agathe sourit. Ses mains sentent le savon.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le miroir est tout embué. Un petit canard jaune attend. Les carreaux sont tièdes. Ça sent un peu le savon. Une petite lampe fait un rond. Le tapis de bain est doux. Une goutte fait ploc. Nina, viens. Le lavabo est prêt. J'arrive, maman. Tu vois le canard jaune ? Oui. Il attend. En ce moment, Nina sort. Elle sort des toilettes. Après les toilettes, on lave. Je prends le savon. Nina ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent la fleur. Ça sent la fleur. Oui. Frotte tes mains. Nina frotte ses mains. Elle frotte le dessus. Elle frotte le dessous. Elle rince. Les bulles partent. Elle essuie. Les mains sont propres. Bravo, Nina. Mes mains sentent la fleur. Oui. C'est le savon. Nina touche le miroir embué. Elle dessine un petit rond. Tu as fait un rond ? Oui, maman. Il est joli. Plus tard, ça sent le repas. La cuisine est un peu chaude. C'est l'heure de manger. Avant de manger, on lave. Je vais au lavabo. Nina ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Savon et eau. Tu as fini tes mains ? Oui, maman. Bravo. Nina regarde ses mains. Ses mains sentent le savon. Le petit canard attend encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
 narrateur|Une petite lampe fait un rond.
 narrateur|Le tapis de bain est doux.
 narrateur|Une goutte fait ploc.
-maman|Nina, je suis près du lavabo.
+maman|Nina, viens. Le lavabo est prêt.
 enfant-f|J'arrive, maman.
 maman|Tu vois le canard jaune ?
 enfant-f|Oui. Il attend.
@@ -1353,9 +1353,13 @@
 narrateur|Elle essuie.
 narrateur|Les mains sont propres.
 maman|Bravo, Nina.
-maman|Tu as fait du bon travail.
 enfant-f|Mes mains sentent la fleur.
 maman|Oui. C'est le savon.
+narrateur|Nina touche le miroir embué.
+narrateur|Elle dessine un petit rond.
+maman|Tu as fait un rond ?
+enfant-f|Oui, maman.
+maman|Il est joli.
 narrateur|Plus tard, ça sent le repas.
 narrateur|La cuisine est un peu chaude.
 maman|C'est l'heure de manger.
@@ -1373,7 +1377,7 @@
 maman|Tu as fini tes mains ?
 enfant-f|Oui, maman.
 maman|Bravo.
-narrateur|Nina sourit.
+narrateur|Nina regarde ses mains.
 narrateur|Ses mains sentent le savon.
 narrateur|Le petit canard attend encore.</t>
         </is>
@@ -1407,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Agathe se lave les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina se lave les mains. Avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1595,7 +1599,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Après les toilettes, Agathe a lavé. Avant de manger, Agathe a lavé. &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt; et eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après les toilettes, Nina a lavé. Avant de manger, Nina a lavé. Savon et eau. Tu te souviens du savon fleur ? Oui. Savon et eau. Bravo, Nina. Le petit canard attend encore. Le miroir est moins embué. Le tapis de bain est encore doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1774,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Agathe s'assoit près de maman. Ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s sont propres.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina s'assoit près de maman. Ses mains sont propres. Tu as les mains propres ? Oui, maman. Bravo. On mange. L'assiette est tiède. Ça sent bon. Mes mains sentent la fleur. Oui. C'est le savon. La petite lampe fait encore un rond.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1945,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nina a lavé après les toilettes. Nina a lavé avant de manger. Bravo, Nina. L'histoire est finie.</t>
+          <t>Nina a lavé après les toilettes. Nina a lavé avant de manger. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a lavé après les toilettes. Nina a lavé avant de manger. Bravo, Nina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2087,8 +2091,7 @@
         <is>
           <t>narrateur|Nina a lavé après les toilettes.
 narrateur|Nina a lavé avant de manger.
-maman|Bravo, Nina.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Nina.</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2154,6 +2157,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>maison, salle d'eau</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agathe, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
